--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:05</t>
+    <t xml:space="preserve">2026-09-24 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -777,10 +777,10 @@
         <v>-0.32</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12">
@@ -846,10 +846,10 @@
         <v>-0.41</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="15">
@@ -1119,13 +1119,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="27">
@@ -1191,10 +1191,10 @@
         <v>-0.42</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30">
@@ -1421,10 +1421,10 @@
         <v>0.54</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="40">
@@ -1444,10 +1444,10 @@
         <v>0.26</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -1513,10 +1513,10 @@
         <v>-0.92</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="44">
@@ -1536,10 +1536,10 @@
         <v>0.74</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="45">
@@ -1766,7 +1766,7 @@
         <v>0.88</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0.75</v>
@@ -1812,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="57">
@@ -1881,10 +1881,10 @@
         <v>0.78</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="60">
@@ -2088,7 +2088,7 @@
         <v>-0.3</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>-0.28</v>
@@ -2111,7 +2111,7 @@
         <v>-0.56</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>-0.37</v>
@@ -2154,13 +2154,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="72">
@@ -2433,10 +2433,10 @@
         <v>-0.51</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="84">
@@ -2456,10 +2456,10 @@
         <v>-0.05</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="85">
@@ -2499,7 +2499,7 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>-0.12</v>
@@ -2801,10 +2801,10 @@
         <v>-0.86</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="100">
@@ -2824,10 +2824,10 @@
         <v>-0.33</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="101">
@@ -2844,13 +2844,13 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="102">
@@ -2893,10 +2893,10 @@
         <v>-0.01</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="104">
@@ -2916,10 +2916,10 @@
         <v>-0.53</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="105">
@@ -3189,10 +3189,10 @@
         <v>18</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>-0.11</v>
@@ -3238,10 +3238,10 @@
         <v>0.34</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="119">
@@ -3261,10 +3261,10 @@
         <v>-0.75</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="120">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:55</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_tarapaca.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
